--- a/analysis/Task_Time_Accuracy.xlsx
+++ b/analysis/Task_Time_Accuracy.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Github\PerspectAR\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E044E7-B652-4E33-8FD3-827B922F3CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18A7499-3FD6-41FA-92E7-2757C151D51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -67,7 +78,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,6 +90,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -104,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -116,6 +133,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,11 +454,11 @@
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2">
-        <v>33.33</v>
+      <c r="D2" s="5">
+        <v>33.333333333333329</v>
       </c>
       <c r="E2">
-        <v>484.21699999999998</v>
+        <v>866.67100000000005</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>9</v>
@@ -456,11 +474,11 @@
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3">
-        <v>91.66</v>
+      <c r="D3" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E3">
-        <v>620.50199999999995</v>
+        <v>743.96500000000003</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>9</v>
@@ -476,11 +494,11 @@
       <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>83.33</v>
+      <c r="D4" s="5">
+        <v>16.666666666666664</v>
       </c>
       <c r="E4">
-        <v>866.67100000000005</v>
+        <v>484.21699999999998</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>6</v>
@@ -496,11 +514,11 @@
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D5">
-        <v>91.66</v>
+      <c r="D5" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E5">
-        <v>743.96500000000003</v>
+        <v>620.50199999999995</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>6</v>
@@ -516,8 +534,8 @@
       <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D6">
-        <v>33.33</v>
+      <c r="D6" s="5">
+        <v>33.333333333333329</v>
       </c>
       <c r="E6">
         <v>683.84400000000005</v>
@@ -536,8 +554,8 @@
       <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="2">
-        <v>91.66</v>
+      <c r="D7" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E7" s="3">
         <v>1146.8779999999999</v>
@@ -556,8 +574,8 @@
       <c r="C8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D8">
-        <v>50</v>
+      <c r="D8" s="5">
+        <v>33.333333333333329</v>
       </c>
       <c r="E8">
         <v>307.541</v>
@@ -576,8 +594,8 @@
       <c r="C9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="2">
-        <v>91.66</v>
+      <c r="D9" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E9">
         <v>728.43600000000004</v>
@@ -596,8 +614,8 @@
       <c r="C10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D10">
-        <v>66.66</v>
+      <c r="D10" s="5">
+        <v>66.666666666666657</v>
       </c>
       <c r="E10">
         <v>784.21500000000003</v>
@@ -616,7 +634,7 @@
       <c r="C11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="5">
         <v>75</v>
       </c>
       <c r="E11">
@@ -636,7 +654,7 @@
       <c r="C12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="5">
         <v>100</v>
       </c>
       <c r="E12">
@@ -656,8 +674,8 @@
       <c r="C13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="2">
-        <v>91.66</v>
+      <c r="D13" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E13">
         <v>430.48500000000001</v>
@@ -676,8 +694,8 @@
       <c r="C14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D14">
-        <v>16.66</v>
+      <c r="D14" s="5">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <v>1032.6279999999999</v>
@@ -696,8 +714,8 @@
       <c r="C15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="2">
-        <v>91.66</v>
+      <c r="D15" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E15">
         <v>841.82399999999996</v>
@@ -716,8 +734,8 @@
       <c r="C16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D16">
-        <v>83.33</v>
+      <c r="D16" s="5">
+        <v>83.333333333333343</v>
       </c>
       <c r="E16">
         <v>594.04399999999998</v>
@@ -736,8 +754,8 @@
       <c r="C17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="2">
-        <v>91.66</v>
+      <c r="D17" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E17">
         <v>423.97800000000001</v>
@@ -756,8 +774,8 @@
       <c r="C18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="4">
-        <v>66.66</v>
+      <c r="D18" s="5">
+        <v>66.666666666666657</v>
       </c>
       <c r="E18" s="3">
         <v>1068.8050000000001</v>
@@ -776,8 +794,8 @@
       <c r="C19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="2">
-        <v>91.66</v>
+      <c r="D19" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E19">
         <v>847.63</v>
@@ -796,8 +814,8 @@
       <c r="C20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="2">
-        <v>50</v>
+      <c r="D20" s="5">
+        <v>66.666666666666657</v>
       </c>
       <c r="E20">
         <v>655.44399999999996</v>
@@ -816,8 +834,8 @@
       <c r="C21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="2">
-        <v>91.66</v>
+      <c r="D21" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E21">
         <v>581.375</v>
@@ -836,8 +854,8 @@
       <c r="C22" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="4">
-        <v>66.66</v>
+      <c r="D22" s="5">
+        <v>66.666666666666657</v>
       </c>
       <c r="E22" s="4">
         <v>770.53399999999999</v>
@@ -856,7 +874,7 @@
       <c r="C23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="5">
         <v>100</v>
       </c>
       <c r="E23" s="2">
@@ -876,8 +894,8 @@
       <c r="C24" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="2">
-        <v>50</v>
+      <c r="D24" s="5">
+        <v>66.666666666666657</v>
       </c>
       <c r="E24" s="2">
         <v>420.40199999999999</v>
@@ -896,8 +914,8 @@
       <c r="C25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="2">
-        <v>91.66</v>
+      <c r="D25" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E25" s="2">
         <v>584.52599999999995</v>
@@ -916,8 +934,8 @@
       <c r="C26" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="2">
-        <v>83.33</v>
+      <c r="D26" s="5">
+        <v>50</v>
       </c>
       <c r="E26" s="3">
         <v>1147.3879999999999</v>
@@ -936,8 +954,8 @@
       <c r="C27" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="2">
-        <v>91.66</v>
+      <c r="D27" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E27">
         <v>818.71699999999998</v>
@@ -956,8 +974,8 @@
       <c r="C28" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D28">
-        <v>50</v>
+      <c r="D28" s="5">
+        <v>33.333333333333329</v>
       </c>
       <c r="E28">
         <v>686.46600000000001</v>
@@ -976,8 +994,8 @@
       <c r="C29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="2">
-        <v>91.66</v>
+      <c r="D29" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E29">
         <v>845.06</v>
@@ -996,8 +1014,8 @@
       <c r="C30" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D30" s="4">
-        <v>66.66</v>
+      <c r="D30" s="5">
+        <v>66.666666666666657</v>
       </c>
       <c r="E30" s="3">
         <v>1197.6610000000001</v>
@@ -1016,7 +1034,7 @@
       <c r="C31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="5">
         <v>100</v>
       </c>
       <c r="E31">
@@ -1036,8 +1054,8 @@
       <c r="C32" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D32">
-        <v>83.33</v>
+      <c r="D32" s="5">
+        <v>83.333333333333343</v>
       </c>
       <c r="E32" s="3">
         <v>971.17399999999998</v>
@@ -1056,8 +1074,8 @@
       <c r="C33" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D33" s="2">
-        <v>91.66</v>
+      <c r="D33" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E33">
         <v>848.28599999999994</v>
@@ -1076,8 +1094,8 @@
       <c r="C34" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D34">
-        <v>66.66</v>
+      <c r="D34" s="5">
+        <v>66.666666666666657</v>
       </c>
       <c r="E34" s="3">
         <v>1089.8130000000001</v>
@@ -1096,7 +1114,7 @@
       <c r="C35" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="5">
         <v>100</v>
       </c>
       <c r="E35">
@@ -1116,8 +1134,8 @@
       <c r="C36" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D36">
-        <v>66.66</v>
+      <c r="D36" s="5">
+        <v>66.666666666666657</v>
       </c>
       <c r="E36">
         <v>854.86900000000003</v>
@@ -1136,8 +1154,8 @@
       <c r="C37" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D37">
-        <v>91.66</v>
+      <c r="D37" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E37">
         <v>766.88900000000001</v>
@@ -1156,8 +1174,8 @@
       <c r="C38" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D38">
-        <v>66.66</v>
+      <c r="D38" s="5">
+        <v>83.333333333333343</v>
       </c>
       <c r="E38">
         <v>762.33</v>
@@ -1176,7 +1194,7 @@
       <c r="C39" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="5">
         <v>100</v>
       </c>
       <c r="E39">
@@ -1196,8 +1214,8 @@
       <c r="C40" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D40">
-        <v>83.33</v>
+      <c r="D40" s="5">
+        <v>83.333333333333343</v>
       </c>
       <c r="E40">
         <v>548.50099999999998</v>
@@ -1216,7 +1234,7 @@
       <c r="C41" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="5">
         <v>100</v>
       </c>
       <c r="E41">
@@ -1236,8 +1254,8 @@
       <c r="C42" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D42">
-        <v>66.66</v>
+      <c r="D42" s="5">
+        <v>66.666666666666657</v>
       </c>
       <c r="E42" s="3">
         <v>1353.0830000000001</v>
@@ -1256,7 +1274,7 @@
       <c r="C43" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="5">
         <v>100</v>
       </c>
       <c r="E43" s="3">
@@ -1276,8 +1294,8 @@
       <c r="C44" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D44">
-        <v>66.66</v>
+      <c r="D44" s="5">
+        <v>66.666666666666657</v>
       </c>
       <c r="E44">
         <v>809.93100000000004</v>
@@ -1296,8 +1314,8 @@
       <c r="C45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D45">
-        <v>91.66</v>
+      <c r="D45" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E45">
         <v>744.28899999999999</v>
@@ -1316,8 +1334,8 @@
       <c r="C46" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D46">
-        <v>50</v>
+      <c r="D46" s="5">
+        <v>66.666666666666657</v>
       </c>
       <c r="E46" s="3">
         <v>1120.9459999999999</v>
@@ -1336,8 +1354,8 @@
       <c r="C47" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D47">
-        <v>91.66</v>
+      <c r="D47" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E47" s="3">
         <v>1044.106</v>
@@ -1356,7 +1374,7 @@
       <c r="C48" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="5">
         <v>50</v>
       </c>
       <c r="E48">
@@ -1376,8 +1394,8 @@
       <c r="C49" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D49">
-        <v>91.66</v>
+      <c r="D49" s="5">
+        <v>91.666666666666657</v>
       </c>
       <c r="E49">
         <v>750.46500000000003</v>

--- a/analysis/Task_Time_Accuracy.xlsx
+++ b/analysis/Task_Time_Accuracy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Github\PerspectAR\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18A7499-3FD6-41FA-92E7-2757C151D51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2640C62B-FF80-44D1-A4B5-7B6729F8627E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
